--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -4582,7 +4582,7 @@
         <v>136409054</v>
       </c>
       <c r="B35" t="n">
-        <v>96450</v>
+        <v>96453</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -4582,7 +4582,7 @@
         <v>136409054</v>
       </c>
       <c r="B35" t="n">
-        <v>96453</v>
+        <v>96454</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -4582,7 +4582,7 @@
         <v>136409054</v>
       </c>
       <c r="B35" t="n">
-        <v>96454</v>
+        <v>96459</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -4582,7 +4582,7 @@
         <v>136409054</v>
       </c>
       <c r="B35" t="n">
-        <v>96459</v>
+        <v>96461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -4582,7 +4582,7 @@
         <v>136409054</v>
       </c>
       <c r="B35" t="n">
-        <v>96461</v>
+        <v>96467</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -4582,7 +4582,7 @@
         <v>136409054</v>
       </c>
       <c r="B35" t="n">
-        <v>96467</v>
+        <v>96469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/S 9899-2021 artfynd.xlsx
+++ b/artfynd/S 9899-2021 artfynd.xlsx
@@ -4582,7 +4582,7 @@
         <v>136409054</v>
       </c>
       <c r="B35" t="n">
-        <v>96469</v>
+        <v>96470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
